--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10804072-6FB3-4FED-A533-CD831E1367DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60EF3A4C-335E-4802-9FC2-3CBC87BC3614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1983,7 +1983,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ED39F3-6BDF-49CE-89F6-820080A68E0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB331AFF-AE1D-47CB-8429-0F2FD4188634}">
   <dimension ref="A9:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2051,7 +2051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4CD4ED-969A-49B1-BD1E-76B81A3F0D82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021E809D-97EB-4CB2-A2E9-CA8D156BE787}">
   <dimension ref="B9:O322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10849,7 +10849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58611AC6-7C35-4FE9-83DC-A6D49260298A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9F4D56-0CEF-4991-BA9F-9B92F42C850C}">
   <dimension ref="B9:AF179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19015,7 +19015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB849468-54E5-4466-83C6-4E177D391D73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FAE78C-E2B5-462A-99D4-91FAD75A86E6}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19326,7 +19326,7 @@
         <v>41</v>
       </c>
       <c r="R18">
-        <v>0.58909999999999996</v>
+        <v>0.58910000000000007</v>
       </c>
       <c r="S18" t="s">
         <v>413</v>
@@ -19382,7 +19382,7 @@
         <v>41</v>
       </c>
       <c r="R22">
-        <v>0.53420000000000001</v>
+        <v>0.5341999999999999</v>
       </c>
       <c r="S22" t="s">
         <v>413</v>
@@ -19466,7 +19466,7 @@
         <v>41</v>
       </c>
       <c r="R28">
-        <v>0.49815000000000004</v>
+        <v>0.49814999999999993</v>
       </c>
       <c r="S28" t="s">
         <v>413</v>
@@ -19522,7 +19522,7 @@
         <v>41</v>
       </c>
       <c r="R32">
-        <v>0.48338333333333333</v>
+        <v>0.48338333333333328</v>
       </c>
       <c r="S32" t="s">
         <v>413</v>
@@ -19606,7 +19606,7 @@
         <v>41</v>
       </c>
       <c r="R38">
-        <v>0.49171666666666658</v>
+        <v>0.49171666666666664</v>
       </c>
       <c r="S38" t="s">
         <v>413</v>
@@ -19718,7 +19718,7 @@
         <v>41</v>
       </c>
       <c r="R46">
-        <v>0.47724999999999995</v>
+        <v>0.47725000000000001</v>
       </c>
       <c r="S46" t="s">
         <v>413</v>
@@ -19802,7 +19802,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.40984999999999988</v>
+        <v>0.40984999999999999</v>
       </c>
       <c r="S52" t="s">
         <v>413</v>
@@ -19830,7 +19830,7 @@
         <v>41</v>
       </c>
       <c r="R54">
-        <v>0.43111666666666665</v>
+        <v>0.43111666666666659</v>
       </c>
       <c r="S54" t="s">
         <v>413</v>
@@ -19858,7 +19858,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.41776666666666662</v>
+        <v>0.41776666666666668</v>
       </c>
       <c r="S56" t="s">
         <v>413</v>
@@ -19942,7 +19942,7 @@
         <v>41</v>
       </c>
       <c r="R62">
-        <v>0.50286666666666657</v>
+        <v>0.50286666666666668</v>
       </c>
       <c r="S62" t="s">
         <v>413</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60EF3A4C-335E-4802-9FC2-3CBC87BC3614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EEC76D-C514-4CC8-95F2-C66E40E7801A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="414">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -1254,7 +1251,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S1aH2</t>
+    <t>S1aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
@@ -1421,19 +1418,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1757,9 +1741,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_04")</f>
-        <v>ts_04</v>
+      <c r="A10" t="s">
+        <v>43</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1887,7 +1870,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S1aH2</v>
+        <v>S1aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1983,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB331AFF-AE1D-47CB-8429-0F2FD4188634}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91172485-2F84-4588-948B-4C057ECE7061}">
   <dimension ref="A9:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2014,10 +1997,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -2051,7 +2030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021E809D-97EB-4CB2-A2E9-CA8D156BE787}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9186DA69-C648-4024-B971-0BC399A60B31}">
   <dimension ref="B9:O322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10849,7 +10828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9F4D56-0CEF-4991-BA9F-9B92F42C850C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8FA786-A189-4CC8-B9C7-0722C0E39A01}">
   <dimension ref="B9:AF179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19015,7 +18994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FAE78C-E2B5-462A-99D4-91FAD75A86E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D4A47A-C48A-4174-ABD6-009B903012BF}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19085,10 +19064,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>0.24931506849315069</v>
       </c>
@@ -19382,7 +19357,7 @@
         <v>41</v>
       </c>
       <c r="R22">
-        <v>0.5341999999999999</v>
+        <v>0.53420000000000001</v>
       </c>
       <c r="S22" t="s">
         <v>413</v>
@@ -19396,7 +19371,7 @@
         <v>37</v>
       </c>
       <c r="R23">
-        <v>0.28840000000000005</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="S23" t="s">
         <v>413</v>
@@ -19522,7 +19497,7 @@
         <v>41</v>
       </c>
       <c r="R32">
-        <v>0.48338333333333328</v>
+        <v>0.48338333333333333</v>
       </c>
       <c r="S32" t="s">
         <v>413</v>
@@ -19578,7 +19553,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.49989999999999996</v>
+        <v>0.49990000000000001</v>
       </c>
       <c r="S36" t="s">
         <v>413</v>
@@ -19662,7 +19637,7 @@
         <v>41</v>
       </c>
       <c r="R42">
-        <v>0.49420000000000003</v>
+        <v>0.49419999999999997</v>
       </c>
       <c r="S42" t="s">
         <v>413</v>
@@ -19704,7 +19679,7 @@
         <v>37</v>
       </c>
       <c r="R45">
-        <v>0.2932333333333334</v>
+        <v>0.29323333333333335</v>
       </c>
       <c r="S45" t="s">
         <v>413</v>
@@ -19802,7 +19777,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.40984999999999999</v>
+        <v>0.40985000000000005</v>
       </c>
       <c r="S52" t="s">
         <v>413</v>
@@ -19830,7 +19805,7 @@
         <v>41</v>
       </c>
       <c r="R54">
-        <v>0.43111666666666659</v>
+        <v>0.43111666666666665</v>
       </c>
       <c r="S54" t="s">
         <v>413</v>
@@ -19984,7 +19959,7 @@
         <v>37</v>
       </c>
       <c r="R65">
-        <v>0.28531666666666666</v>
+        <v>0.28531666666666672</v>
       </c>
       <c r="S65" t="s">
         <v>413</v>
@@ -20012,7 +19987,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.29196666666666665</v>
+        <v>0.29196666666666671</v>
       </c>
       <c r="S67" t="s">
         <v>413</v>
@@ -20026,7 +20001,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.50366666666666671</v>
+        <v>0.5036666666666666</v>
       </c>
       <c r="S68" t="s">
         <v>413</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EEC76D-C514-4CC8-95F2-C66E40E7801A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6494B265-E6DE-4443-969C-0BD86D5F1996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1257,7 +1257,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S1aH1</t>
+    <t>S1aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S1aH1</v>
+        <v>S1aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1966,7 +1966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91172485-2F84-4588-948B-4C057ECE7061}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125F65B3-1DAA-45E0-8DCB-78E3737D6A9A}">
   <dimension ref="A9:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2030,7 +2030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9186DA69-C648-4024-B971-0BC399A60B31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE0DC60-48E9-4B6E-BF02-526C4D0812BA}">
   <dimension ref="B9:O322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10828,7 +10828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8FA786-A189-4CC8-B9C7-0722C0E39A01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE47EF85-7028-4DCA-96C5-C82663487E5E}">
   <dimension ref="B9:AF179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18994,7 +18994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D4A47A-C48A-4174-ABD6-009B903012BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E7C537-C745-4E6F-81C2-93E4AB2BDE3E}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19180,7 +19180,7 @@
         <v>37</v>
       </c>
       <c r="R13">
-        <v>0.26947758574177361</v>
+        <v>0.26947758574177366</v>
       </c>
       <c r="S13" t="s">
         <v>413</v>
@@ -19261,7 +19261,7 @@
         <v>41</v>
       </c>
       <c r="R16">
-        <v>0.54009341110043374</v>
+        <v>0.54009341110043385</v>
       </c>
       <c r="S16" t="s">
         <v>413</v>
@@ -19315,7 +19315,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.31741666666666662</v>
+        <v>0.31741666666666668</v>
       </c>
       <c r="S19" t="s">
         <v>413</v>
@@ -19329,7 +19329,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.57326666666666659</v>
+        <v>0.5732666666666667</v>
       </c>
       <c r="S20" t="s">
         <v>413</v>
@@ -19413,7 +19413,7 @@
         <v>41</v>
       </c>
       <c r="R26">
-        <v>0.48621666666666669</v>
+        <v>0.48621666666666657</v>
       </c>
       <c r="S26" t="s">
         <v>413</v>
@@ -19427,7 +19427,7 @@
         <v>37</v>
       </c>
       <c r="R27">
-        <v>0.29241666666666666</v>
+        <v>0.29241666666666671</v>
       </c>
       <c r="S27" t="s">
         <v>413</v>
@@ -19441,7 +19441,7 @@
         <v>41</v>
       </c>
       <c r="R28">
-        <v>0.49814999999999993</v>
+        <v>0.49815000000000004</v>
       </c>
       <c r="S28" t="s">
         <v>413</v>
@@ -19497,7 +19497,7 @@
         <v>41</v>
       </c>
       <c r="R32">
-        <v>0.48338333333333333</v>
+        <v>0.48338333333333328</v>
       </c>
       <c r="S32" t="s">
         <v>413</v>
@@ -19553,7 +19553,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.49990000000000001</v>
+        <v>0.49989999999999996</v>
       </c>
       <c r="S36" t="s">
         <v>413</v>
@@ -19567,7 +19567,7 @@
         <v>37</v>
       </c>
       <c r="R37">
-        <v>0.28526666666666667</v>
+        <v>0.28526666666666672</v>
       </c>
       <c r="S37" t="s">
         <v>413</v>
@@ -19679,7 +19679,7 @@
         <v>37</v>
       </c>
       <c r="R45">
-        <v>0.29323333333333335</v>
+        <v>0.2932333333333334</v>
       </c>
       <c r="S45" t="s">
         <v>413</v>
@@ -19693,7 +19693,7 @@
         <v>41</v>
       </c>
       <c r="R46">
-        <v>0.47725000000000001</v>
+        <v>0.47724999999999995</v>
       </c>
       <c r="S46" t="s">
         <v>413</v>
@@ -19735,7 +19735,7 @@
         <v>37</v>
       </c>
       <c r="R49">
-        <v>0.23878333333333335</v>
+        <v>0.23878333333333332</v>
       </c>
       <c r="S49" t="s">
         <v>413</v>
@@ -19749,7 +19749,7 @@
         <v>41</v>
       </c>
       <c r="R50">
-        <v>0.42483333333333334</v>
+        <v>0.4248333333333334</v>
       </c>
       <c r="S50" t="s">
         <v>413</v>
@@ -19777,7 +19777,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.40985000000000005</v>
+        <v>0.40984999999999999</v>
       </c>
       <c r="S52" t="s">
         <v>413</v>
@@ -19931,7 +19931,7 @@
         <v>37</v>
       </c>
       <c r="R63">
-        <v>0.28906666666666669</v>
+        <v>0.28906666666666664</v>
       </c>
       <c r="S63" t="s">
         <v>413</v>
@@ -19959,7 +19959,7 @@
         <v>37</v>
       </c>
       <c r="R65">
-        <v>0.28531666666666672</v>
+        <v>0.28531666666666666</v>
       </c>
       <c r="S65" t="s">
         <v>413</v>
@@ -19987,7 +19987,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.29196666666666671</v>
+        <v>0.29196666666666665</v>
       </c>
       <c r="S67" t="s">
         <v>413</v>
@@ -20001,7 +20001,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.5036666666666666</v>
+        <v>0.50366666666666671</v>
       </c>
       <c r="S68" t="s">
         <v>413</v>
